--- a/output/graficos_dimensiones/comunal_i_ingr_a_2021_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2021_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:09</t>
+    <t xml:space="preserve">2026-09-09 23:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2021_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2021_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:03</t>
+    <t xml:space="preserve">2026-09-17 14:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2021_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2021_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:00</t>
+    <t xml:space="preserve">2026-09-23 12:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2021_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2021_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:29</t>
+    <t xml:space="preserve">2026-10-02 14:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2021_los lagos.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2021_los lagos.xlsx
@@ -135,7 +135,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:14</t>
+    <t xml:space="preserve">2026-10-05 10:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -741,7 +741,7 @@
         <v>2021</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>804405.12</v>
+        <v>804405.13</v>
       </c>
     </row>
     <row r="13">
@@ -911,7 +911,7 @@
         <v>2021</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>723181.62</v>
+        <v>723181.63</v>
       </c>
     </row>
     <row r="23">
